--- a/artfynd/A 63262-2025 artfynd.xlsx
+++ b/artfynd/A 63262-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370633</v>
       </c>
       <c r="B2" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370618</v>
       </c>
       <c r="B3" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370625</v>
       </c>
       <c r="B4" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370677</v>
       </c>
       <c r="B5" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370519</v>
       </c>
       <c r="B6" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370931</v>
       </c>
       <c r="B7" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63262-2025 artfynd.xlsx
+++ b/artfynd/A 63262-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370633</v>
       </c>
       <c r="B2" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370618</v>
       </c>
       <c r="B3" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370625</v>
       </c>
       <c r="B4" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370677</v>
       </c>
       <c r="B5" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370519</v>
       </c>
       <c r="B6" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370931</v>
       </c>
       <c r="B7" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63262-2025 artfynd.xlsx
+++ b/artfynd/A 63262-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370633</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370618</v>
       </c>
       <c r="B3" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370625</v>
       </c>
       <c r="B4" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370677</v>
       </c>
       <c r="B5" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370519</v>
       </c>
       <c r="B6" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370931</v>
       </c>
       <c r="B7" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63262-2025 artfynd.xlsx
+++ b/artfynd/A 63262-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370633</v>
       </c>
       <c r="B2" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370618</v>
       </c>
       <c r="B3" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370625</v>
       </c>
       <c r="B4" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370677</v>
       </c>
       <c r="B5" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370519</v>
       </c>
       <c r="B6" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370931</v>
       </c>
       <c r="B7" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63262-2025 artfynd.xlsx
+++ b/artfynd/A 63262-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370633</v>
       </c>
       <c r="B2" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370618</v>
       </c>
       <c r="B3" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370625</v>
       </c>
       <c r="B4" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370677</v>
       </c>
       <c r="B5" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370519</v>
       </c>
       <c r="B6" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370931</v>
       </c>
       <c r="B7" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63262-2025 artfynd.xlsx
+++ b/artfynd/A 63262-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370633</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137370618</v>
       </c>
       <c r="B3" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137370625</v>
       </c>
       <c r="B4" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137370677</v>
       </c>
       <c r="B5" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137370519</v>
       </c>
       <c r="B6" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137370931</v>
       </c>
       <c r="B7" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
